--- a/docs/f3.m3.pp_formato_solicitud_desvinculacion_de_beneficiarios_v4.xlsx
+++ b/docs/f3.m3.pp_formato_solicitud_desvinculacion_de_beneficiarios_v4.xlsx
@@ -1,26 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FF867B3-36AD-4B21-A775-22A28A73E772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="FORMATO" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="INSTRUCCIONES" state="visible" r:id="rId5"/>
+    <sheet name="FORMATO" sheetId="1" r:id="rId1"/>
+    <sheet name="INSTRUCCIONES" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase">FORMATO!$A$3:$W$3</definedName>
   </definedNames>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="95">
-  <si>
-    <t xml:space="preserve">PROCESO
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="84">
+  <si>
+    <t>PROCESO
 PROMOCIÓN Y PREVENCIÓN
 FORMATO SOLICITUD DESVINCULACIÓN DE BENEFICIARIOS</t>
   </si>
@@ -34,7 +46,7 @@
     <t>Página 1 de 1</t>
   </si>
   <si>
-    <t xml:space="preserve">Clasificación de la Información:
+    <t>Clasificación de la Información:
 Clasificada</t>
   </si>
   <si>
@@ -117,39 +129,6 @@
   </si>
   <si>
     <t>BOGOTA</t>
-  </si>
-  <si>
-    <t>800112895</t>
-  </si>
-  <si>
-    <t>ASOCIACION DE PADRES USUARIOS DE LOS HOGARES DE BIENESTAR BARRIO UNIDOS DEL NORTE DE SAN CRISTOBAL</t>
-  </si>
-  <si>
-    <t>11028092024</t>
-  </si>
-  <si>
-    <t>FUNDACION SOCIAL Y EDUCATIVA WESLEYANA NORTE</t>
-  </si>
-  <si>
-    <t>11023482025</t>
-  </si>
-  <si>
-    <t>1100100134296</t>
-  </si>
-  <si>
-    <t>CENTRO DE DESARROLLO INFANTIL VIDA INTEGRAL II</t>
-  </si>
-  <si>
-    <t>RC</t>
-  </si>
-  <si>
-    <t>1020851871</t>
-  </si>
-  <si>
-    <t>ROSNIER JEREMIAS VARGAS MENDOZA</t>
-  </si>
-  <si>
-    <t>01/07/2026</t>
   </si>
   <si>
     <t>Antes de imprimir este documento… piense en el medio ambiente!</t>
@@ -176,19 +155,19 @@
     <r>
       <rPr>
         <b/>
+        <sz val="10"/>
         <color rgb="FF000000"/>
+        <rFont val="Arial"/>
         <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
       </rPr>
       <t>Copia del documento de identidad</t>
     </r>
     <r>
       <rPr>
+        <sz val="10"/>
         <color rgb="FF000000"/>
+        <rFont val="Arial"/>
         <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
       </rPr>
       <t xml:space="preserve"> ( LEGIBLE) en formato PDF  
 * </t>
@@ -196,19 +175,19 @@
     <r>
       <rPr>
         <b/>
+        <sz val="10"/>
         <color rgb="FF000000"/>
+        <rFont val="Arial"/>
         <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
       </rPr>
       <t>Listado de asistencia RAM</t>
     </r>
     <r>
       <rPr>
+        <sz val="10"/>
         <color rgb="FF000000"/>
+        <rFont val="Arial"/>
         <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
       </rPr>
       <t xml:space="preserve"> ( LEGIBLE) en FORMATO PDF
 Si desea tambien puede enviar como soporte una carta firmada por el acudiente solicitando la atención e indicando que no está siendo atendido en ningún otro programa de primera infancia.</t>
@@ -220,19 +199,19 @@
     </r>
     <r>
       <rPr>
+        <sz val="10"/>
         <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
         <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
       </rPr>
       <t>5 días hábiles</t>
     </r>
     <r>
       <rPr>
+        <sz val="10"/>
         <color rgb="FF000000"/>
+        <rFont val="Arial"/>
         <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
       </rPr>
       <t xml:space="preserve"> contados a partir del momento de que usted envie el correo electronico con los soportes completos.</t>
     </r>
@@ -243,10 +222,10 @@
         <b/>
         <i/>
         <u/>
+        <sz val="10"/>
         <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
         <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
       </rPr>
       <t>IMPORTANTE TENER EN CUENTA:</t>
     </r>
@@ -254,19 +233,19 @@
       <rPr>
         <i/>
         <u/>
+        <sz val="10"/>
         <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
         <family val="2"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
       </rPr>
       <t xml:space="preserve">
 </t>
     </r>
     <r>
       <rPr>
-        <family val="2"/>
         <sz val="10"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">
 </t>
@@ -274,18 +253,18 @@
     <r>
       <rPr>
         <b/>
-        <family val="2"/>
         <sz val="10"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">
 * Solo se procedera con los casos que cuenten con los soportes completos, legibles y oportunos.</t>
     </r>
     <r>
       <rPr>
-        <family val="2"/>
         <sz val="10"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">
 Si va adjuntar varios documentos de identidad por favor nombrarlos con el numero de documento de identidad del beneficiario, asi logramos atender la solicitud en el menor tiempo posible.
@@ -428,128 +407,150 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="18" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="11"/>
-      <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <family val="2"/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color theme="0"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="11"/>
-      <name val="Arial"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="11"/>
-      <name val="Arial"/>
     </font>
     <font>
       <b/>
       <i/>
       <u/>
+      <sz val="11"/>
       <color theme="0"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="11"/>
-      <name val="Arial"/>
     </font>
     <font>
       <b/>
       <i/>
+      <sz val="11"/>
       <color theme="0"/>
+      <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Arial"/>
-    </font>
-    <font>
       <family val="2"/>
-      <sz val="11"/>
-      <name val="Arial"/>
     </font>
     <font>
       <b/>
+      <sz val="12"/>
       <color theme="1"/>
+      <name val="Tempus Sans ITC"/>
       <family val="5"/>
-      <sz val="12"/>
-      <name val="Tempus Sans ITC"/>
     </font>
     <font>
       <b/>
+      <sz val="6"/>
       <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="6"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
       <sz val="10"/>
       <name val="Arial"/>
-    </font>
-    <font>
       <family val="2"/>
-      <sz val="10"/>
-      <name val="Arial"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="10"/>
-      <name val="Arial"/>
     </font>
     <font>
       <i/>
       <u/>
+      <sz val="10"/>
       <color rgb="FFFF0000"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="10"/>
-      <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <family val="5"/>
       <sz val="12"/>
       <name val="Tempus Sans ITC"/>
+      <family val="5"/>
     </font>
     <font>
       <b/>
-      <family val="2"/>
       <sz val="6"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -567,7 +568,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.5999938962981048"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -892,71 +893,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1050,27 +991,99 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1091,12 +1104,6 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1132,7 +1139,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Picture 1">
+        <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
@@ -1181,10 +1188,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Picture 1">
+        <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1499,9 +1506,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:W23"/>
-  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="11.42578125" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="32" style="1" customWidth="1"/>
     <col min="3" max="3" width="27.42578125" style="1" customWidth="1"/>
@@ -1518,1242 +1525,1106 @@
     <col min="21" max="22" width="25" style="1" customWidth="1"/>
     <col min="23" max="23" width="29" style="1" customWidth="1"/>
     <col min="24" max="24" width="52.5703125" style="1" customWidth="1"/>
-    <col min="25" max="16384" width="11.42578125" style="1" customWidth="1"/>
+    <col min="25" max="25" width="11.42578125" style="1" customWidth="1"/>
+    <col min="26" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.15" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A1" s="2"/>
-      <c r="B1" s="3" t="s">
+    <row r="1" spans="1:23" ht="31.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="45"/>
+      <c r="B1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="4"/>
-      <c r="R1" s="4"/>
-      <c r="S1" s="4"/>
-      <c r="T1" s="5"/>
-      <c r="U1" s="6" t="s">
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="39"/>
+      <c r="M1" s="39"/>
+      <c r="N1" s="39"/>
+      <c r="O1" s="39"/>
+      <c r="P1" s="39"/>
+      <c r="Q1" s="39"/>
+      <c r="R1" s="39"/>
+      <c r="S1" s="39"/>
+      <c r="T1" s="40"/>
+      <c r="U1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="V1" s="7">
+      <c r="V1" s="44">
         <v>44728</v>
       </c>
-      <c r="W1" s="7"/>
-    </row>
-    <row r="2" ht="28.9" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A2" s="2"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="5"/>
-      <c r="U2" s="6" t="s">
+      <c r="W1" s="44"/>
+    </row>
+    <row r="2" spans="1:23" ht="28.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="45"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
+      <c r="K2" s="39"/>
+      <c r="L2" s="39"/>
+      <c r="M2" s="39"/>
+      <c r="N2" s="39"/>
+      <c r="O2" s="39"/>
+      <c r="P2" s="39"/>
+      <c r="Q2" s="39"/>
+      <c r="R2" s="39"/>
+      <c r="S2" s="39"/>
+      <c r="T2" s="40"/>
+      <c r="U2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="V2" s="6" t="s">
+      <c r="V2" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="W2" s="6"/>
-    </row>
-    <row r="3" ht="36" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A3" s="2"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="9"/>
-      <c r="R3" s="9"/>
-      <c r="S3" s="9"/>
-      <c r="T3" s="10"/>
-      <c r="U3" s="11" t="s">
+      <c r="W2" s="46"/>
+    </row>
+    <row r="3" spans="1:23" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="45"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="42"/>
+      <c r="K3" s="42"/>
+      <c r="L3" s="42"/>
+      <c r="M3" s="42"/>
+      <c r="N3" s="42"/>
+      <c r="O3" s="42"/>
+      <c r="P3" s="42"/>
+      <c r="Q3" s="42"/>
+      <c r="R3" s="42"/>
+      <c r="S3" s="42"/>
+      <c r="T3" s="43"/>
+      <c r="U3" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="V3" s="11"/>
-      <c r="W3" s="11"/>
-    </row>
-    <row r="4" ht="28.15" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A4" s="12"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="14" t="s">
+      <c r="V3" s="47"/>
+      <c r="W3" s="47"/>
+    </row>
+    <row r="4" spans="1:23" ht="28.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="48"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="17" t="s">
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="52"/>
+      <c r="J4" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="19"/>
-      <c r="N4" s="20" t="s">
+      <c r="K4" s="54"/>
+      <c r="L4" s="54"/>
+      <c r="M4" s="55"/>
+      <c r="N4" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="O4" s="21"/>
-      <c r="P4" s="21"/>
-      <c r="Q4" s="21"/>
-      <c r="R4" s="21"/>
-      <c r="S4" s="21"/>
-      <c r="T4" s="21"/>
-      <c r="U4" s="21"/>
-      <c r="V4" s="21"/>
-      <c r="W4" s="22"/>
-    </row>
-    <row r="5" ht="69" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A5" s="23" t="s">
+      <c r="O4" s="57"/>
+      <c r="P4" s="57"/>
+      <c r="Q4" s="57"/>
+      <c r="R4" s="57"/>
+      <c r="S4" s="57"/>
+      <c r="T4" s="57"/>
+      <c r="U4" s="57"/>
+      <c r="V4" s="57"/>
+      <c r="W4" s="58"/>
+    </row>
+    <row r="5" spans="1:23" ht="69" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="23" t="s">
+      <c r="D5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="24" t="s">
+      <c r="E5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="24" t="s">
+      <c r="F5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="24" t="s">
+      <c r="G5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="24" t="s">
+      <c r="H5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I5" s="24" t="s">
+      <c r="I5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="J5" s="24" t="s">
+      <c r="J5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="K5" s="24" t="s">
+      <c r="K5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="L5" s="24" t="s">
+      <c r="L5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="M5" s="24" t="s">
+      <c r="M5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="N5" s="25" t="s">
+      <c r="N5" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="O5" s="25" t="s">
+      <c r="O5" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="P5" s="25" t="s">
+      <c r="P5" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="Q5" s="25" t="s">
+      <c r="Q5" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="R5" s="25" t="s">
+      <c r="R5" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="S5" s="25" t="s">
+      <c r="S5" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="T5" s="25" t="s">
+      <c r="T5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="U5" s="25" t="s">
+      <c r="U5" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="V5" s="25" t="s">
+      <c r="V5" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="W5" s="25" t="s">
+      <c r="W5" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A6" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="27" t="s">
+    <row r="6" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="6"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="13"/>
+      <c r="N6" s="14"/>
+      <c r="O6" s="15"/>
+      <c r="P6" s="16"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="17"/>
+      <c r="T6" s="18"/>
+      <c r="U6" s="18"/>
+      <c r="V6" s="19"/>
+      <c r="W6" s="20"/>
+    </row>
+    <row r="7" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="6"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="21"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="12"/>
+      <c r="M7" s="13"/>
+      <c r="N7" s="14"/>
+      <c r="O7" s="15"/>
+      <c r="P7" s="16"/>
+      <c r="Q7" s="17"/>
+      <c r="R7" s="17"/>
+      <c r="S7" s="17"/>
+      <c r="T7" s="18"/>
+      <c r="U7" s="18"/>
+      <c r="V7" s="19"/>
+      <c r="W7" s="20"/>
+    </row>
+    <row r="8" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="6"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="13"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="15"/>
+      <c r="P8" s="16"/>
+      <c r="Q8" s="17"/>
+      <c r="R8" s="17"/>
+      <c r="S8" s="17"/>
+      <c r="T8" s="18"/>
+      <c r="U8" s="18"/>
+      <c r="V8" s="19"/>
+      <c r="W8" s="20"/>
+    </row>
+    <row r="9" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="6"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="12"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="14"/>
+      <c r="O9" s="15"/>
+      <c r="P9" s="16"/>
+      <c r="Q9" s="17"/>
+      <c r="R9" s="17"/>
+      <c r="S9" s="17"/>
+      <c r="T9" s="18"/>
+      <c r="U9" s="18"/>
+      <c r="V9" s="19"/>
+      <c r="W9" s="20"/>
+    </row>
+    <row r="10" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="6"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="12"/>
+      <c r="M10" s="13"/>
+      <c r="N10" s="14"/>
+      <c r="O10" s="15"/>
+      <c r="P10" s="16"/>
+      <c r="Q10" s="17"/>
+      <c r="R10" s="17"/>
+      <c r="S10" s="17"/>
+      <c r="T10" s="18"/>
+      <c r="U10" s="18"/>
+      <c r="V10" s="19"/>
+      <c r="W10" s="20"/>
+    </row>
+    <row r="11" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="6"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="12"/>
+      <c r="M11" s="13"/>
+      <c r="N11" s="14"/>
+      <c r="O11" s="15"/>
+      <c r="P11" s="16"/>
+      <c r="Q11" s="17"/>
+      <c r="R11" s="17"/>
+      <c r="S11" s="17"/>
+      <c r="T11" s="18"/>
+      <c r="U11" s="18"/>
+      <c r="V11" s="19"/>
+      <c r="W11" s="20"/>
+    </row>
+    <row r="12" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="6"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="12"/>
+      <c r="M12" s="13"/>
+      <c r="N12" s="14"/>
+      <c r="O12" s="15"/>
+      <c r="P12" s="16"/>
+      <c r="Q12" s="17"/>
+      <c r="R12" s="17"/>
+      <c r="S12" s="17"/>
+      <c r="T12" s="18"/>
+      <c r="U12" s="18"/>
+      <c r="V12" s="19"/>
+      <c r="W12" s="20"/>
+    </row>
+    <row r="13" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="6"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="12"/>
+      <c r="M13" s="13"/>
+      <c r="N13" s="14"/>
+      <c r="O13" s="15"/>
+      <c r="P13" s="16"/>
+      <c r="Q13" s="17"/>
+      <c r="R13" s="17"/>
+      <c r="S13" s="17"/>
+      <c r="T13" s="18"/>
+      <c r="U13" s="18"/>
+      <c r="V13" s="19"/>
+      <c r="W13" s="20"/>
+    </row>
+    <row r="14" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="6"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="12"/>
+      <c r="M14" s="13"/>
+      <c r="N14" s="14"/>
+      <c r="O14" s="15"/>
+      <c r="P14" s="16"/>
+      <c r="Q14" s="17"/>
+      <c r="R14" s="17"/>
+      <c r="S14" s="17"/>
+      <c r="T14" s="18"/>
+      <c r="U14" s="18"/>
+      <c r="V14" s="19"/>
+      <c r="W14" s="20"/>
+    </row>
+    <row r="15" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="6"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="12"/>
+      <c r="M15" s="13"/>
+      <c r="N15" s="14"/>
+      <c r="O15" s="15"/>
+      <c r="P15" s="16"/>
+      <c r="Q15" s="17"/>
+      <c r="R15" s="17"/>
+      <c r="S15" s="17"/>
+      <c r="T15" s="18"/>
+      <c r="U15" s="18"/>
+      <c r="V15" s="19"/>
+      <c r="W15" s="20"/>
+    </row>
+    <row r="16" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="6"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="12"/>
+      <c r="M16" s="13"/>
+      <c r="N16" s="14"/>
+      <c r="O16" s="15"/>
+      <c r="P16" s="16"/>
+      <c r="Q16" s="17"/>
+      <c r="R16" s="17"/>
+      <c r="S16" s="17"/>
+      <c r="T16" s="18"/>
+      <c r="U16" s="18"/>
+      <c r="V16" s="19"/>
+      <c r="W16" s="20"/>
+    </row>
+    <row r="17" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="6"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="12"/>
+      <c r="M17" s="13"/>
+      <c r="N17" s="14"/>
+      <c r="O17" s="15"/>
+      <c r="P17" s="16"/>
+      <c r="Q17" s="17"/>
+      <c r="R17" s="17"/>
+      <c r="S17" s="17"/>
+      <c r="T17" s="18"/>
+      <c r="U17" s="18"/>
+      <c r="V17" s="19"/>
+      <c r="W17" s="20"/>
+    </row>
+    <row r="18" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="6"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="13"/>
+      <c r="N18" s="14"/>
+      <c r="O18" s="15"/>
+      <c r="P18" s="16"/>
+      <c r="Q18" s="17"/>
+      <c r="R18" s="17"/>
+      <c r="S18" s="17"/>
+      <c r="T18" s="18"/>
+      <c r="U18" s="18"/>
+      <c r="V18" s="19"/>
+      <c r="W18" s="20"/>
+    </row>
+    <row r="19" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="6"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="12"/>
+      <c r="M19" s="13"/>
+      <c r="N19" s="14"/>
+      <c r="O19" s="15"/>
+      <c r="P19" s="16"/>
+      <c r="Q19" s="17"/>
+      <c r="R19" s="17"/>
+      <c r="S19" s="17"/>
+      <c r="T19" s="18"/>
+      <c r="U19" s="18"/>
+      <c r="V19" s="19"/>
+      <c r="W19" s="20"/>
+    </row>
+    <row r="20" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="6"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="23"/>
+      <c r="J20" s="25"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="26"/>
+      <c r="M20" s="27"/>
+      <c r="N20" s="14"/>
+      <c r="O20" s="28"/>
+      <c r="P20" s="29"/>
+      <c r="Q20" s="30"/>
+      <c r="R20" s="30"/>
+      <c r="S20" s="30"/>
+      <c r="T20" s="31"/>
+      <c r="U20" s="31"/>
+      <c r="V20" s="32"/>
+      <c r="W20" s="33"/>
+    </row>
+    <row r="21" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="27" t="s">
+      <c r="B21" s="59"/>
+      <c r="C21" s="59"/>
+      <c r="D21" s="59"/>
+      <c r="E21" s="59"/>
+      <c r="F21" s="59"/>
+      <c r="G21" s="59"/>
+      <c r="H21" s="59"/>
+      <c r="I21" s="59"/>
+      <c r="J21" s="59"/>
+      <c r="K21" s="59"/>
+      <c r="L21" s="59"/>
+      <c r="M21" s="59"/>
+      <c r="N21" s="59"/>
+      <c r="O21" s="59"/>
+      <c r="P21" s="59"/>
+      <c r="Q21" s="59"/>
+      <c r="R21" s="59"/>
+      <c r="S21" s="59"/>
+      <c r="T21" s="59"/>
+      <c r="U21" s="59"/>
+      <c r="V21" s="59"/>
+      <c r="W21" s="59"/>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A22" s="60" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="28" t="s">
+      <c r="B22" s="60"/>
+      <c r="C22" s="60"/>
+      <c r="D22" s="60"/>
+      <c r="E22" s="60"/>
+      <c r="F22" s="60"/>
+      <c r="G22" s="60"/>
+      <c r="H22" s="60"/>
+      <c r="I22" s="60"/>
+      <c r="J22" s="60"/>
+      <c r="K22" s="60"/>
+      <c r="L22" s="60"/>
+      <c r="M22" s="60"/>
+      <c r="N22" s="60"/>
+      <c r="O22" s="60"/>
+      <c r="P22" s="60"/>
+      <c r="Q22" s="60"/>
+      <c r="R22" s="60"/>
+      <c r="S22" s="60"/>
+      <c r="T22" s="60"/>
+      <c r="U22" s="60"/>
+      <c r="V22" s="60"/>
+      <c r="W22" s="60"/>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A23" s="60" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" s="30" t="s">
-        <v>35</v>
-      </c>
-      <c r="G6" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="H6" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="I6" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="J6" s="31" t="s">
-        <v>39</v>
-      </c>
-      <c r="K6" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="L6" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="M6" s="33" t="s">
-        <v>42</v>
-      </c>
-      <c r="N6" s="34"/>
-      <c r="O6" s="35"/>
-      <c r="P6" s="36"/>
-      <c r="Q6" s="37"/>
-      <c r="R6" s="37"/>
-      <c r="S6" s="37"/>
-      <c r="T6" s="38"/>
-      <c r="U6" s="38"/>
-      <c r="V6" s="39"/>
-      <c r="W6" s="40"/>
-    </row>
-    <row r="7" ht="15" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A7" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="E7" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" s="30" t="s">
-        <v>35</v>
-      </c>
-      <c r="G7" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="H7" s="41" t="s">
-        <v>37</v>
-      </c>
-      <c r="I7" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="J7" s="31" t="s">
-        <v>39</v>
-      </c>
-      <c r="K7" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="L7" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="M7" s="33" t="s">
-        <v>42</v>
-      </c>
-      <c r="N7" s="34"/>
-      <c r="O7" s="35"/>
-      <c r="P7" s="36"/>
-      <c r="Q7" s="37"/>
-      <c r="R7" s="37"/>
-      <c r="S7" s="37"/>
-      <c r="T7" s="38"/>
-      <c r="U7" s="38"/>
-      <c r="V7" s="39"/>
-      <c r="W7" s="40"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A8" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="F8" s="30" t="s">
-        <v>35</v>
-      </c>
-      <c r="G8" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="H8" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="I8" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="J8" s="31" t="s">
-        <v>39</v>
-      </c>
-      <c r="K8" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="L8" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="M8" s="33" t="s">
-        <v>42</v>
-      </c>
-      <c r="N8" s="34"/>
-      <c r="O8" s="35"/>
-      <c r="P8" s="36"/>
-      <c r="Q8" s="37"/>
-      <c r="R8" s="37"/>
-      <c r="S8" s="37"/>
-      <c r="T8" s="38"/>
-      <c r="U8" s="38"/>
-      <c r="V8" s="39"/>
-      <c r="W8" s="40"/>
-    </row>
-    <row r="9" ht="15" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A9" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="E9" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="F9" s="30" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="H9" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="I9" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="J9" s="31" t="s">
-        <v>39</v>
-      </c>
-      <c r="K9" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="L9" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="M9" s="33" t="s">
-        <v>42</v>
-      </c>
-      <c r="N9" s="34"/>
-      <c r="O9" s="35"/>
-      <c r="P9" s="36"/>
-      <c r="Q9" s="37"/>
-      <c r="R9" s="37"/>
-      <c r="S9" s="37"/>
-      <c r="T9" s="38"/>
-      <c r="U9" s="38"/>
-      <c r="V9" s="39"/>
-      <c r="W9" s="40"/>
-    </row>
-    <row r="10" ht="15" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A10" s="26"/>
-      <c r="B10" s="27"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="28"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="27"/>
-      <c r="H10" s="27"/>
-      <c r="I10" s="28"/>
-      <c r="J10" s="31"/>
-      <c r="K10" s="27"/>
-      <c r="L10" s="32"/>
-      <c r="M10" s="33"/>
-      <c r="N10" s="34"/>
-      <c r="O10" s="35"/>
-      <c r="P10" s="36"/>
-      <c r="Q10" s="37"/>
-      <c r="R10" s="37"/>
-      <c r="S10" s="37"/>
-      <c r="T10" s="38"/>
-      <c r="U10" s="38"/>
-      <c r="V10" s="39"/>
-      <c r="W10" s="40"/>
-    </row>
-    <row r="11" ht="15" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A11" s="26"/>
-      <c r="B11" s="27"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="29"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="27"/>
-      <c r="H11" s="27"/>
-      <c r="I11" s="28"/>
-      <c r="J11" s="31"/>
-      <c r="K11" s="27"/>
-      <c r="L11" s="32"/>
-      <c r="M11" s="33"/>
-      <c r="N11" s="34"/>
-      <c r="O11" s="35"/>
-      <c r="P11" s="36"/>
-      <c r="Q11" s="37"/>
-      <c r="R11" s="37"/>
-      <c r="S11" s="37"/>
-      <c r="T11" s="38"/>
-      <c r="U11" s="38"/>
-      <c r="V11" s="39"/>
-      <c r="W11" s="40"/>
-    </row>
-    <row r="12" ht="15" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A12" s="26"/>
-      <c r="B12" s="27"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="29"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="27"/>
-      <c r="H12" s="27"/>
-      <c r="I12" s="28"/>
-      <c r="J12" s="31"/>
-      <c r="K12" s="27"/>
-      <c r="L12" s="32"/>
-      <c r="M12" s="33"/>
-      <c r="N12" s="34"/>
-      <c r="O12" s="35"/>
-      <c r="P12" s="36"/>
-      <c r="Q12" s="37"/>
-      <c r="R12" s="37"/>
-      <c r="S12" s="37"/>
-      <c r="T12" s="38"/>
-      <c r="U12" s="38"/>
-      <c r="V12" s="39"/>
-      <c r="W12" s="40"/>
-    </row>
-    <row r="13" ht="15" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A13" s="26"/>
-      <c r="B13" s="27"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="27"/>
-      <c r="H13" s="27"/>
-      <c r="I13" s="28"/>
-      <c r="J13" s="31"/>
-      <c r="K13" s="27"/>
-      <c r="L13" s="32"/>
-      <c r="M13" s="33"/>
-      <c r="N13" s="34"/>
-      <c r="O13" s="35"/>
-      <c r="P13" s="36"/>
-      <c r="Q13" s="37"/>
-      <c r="R13" s="37"/>
-      <c r="S13" s="37"/>
-      <c r="T13" s="38"/>
-      <c r="U13" s="38"/>
-      <c r="V13" s="39"/>
-      <c r="W13" s="40"/>
-    </row>
-    <row r="14" ht="15" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A14" s="26"/>
-      <c r="B14" s="27"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="27"/>
-      <c r="I14" s="28"/>
-      <c r="J14" s="31"/>
-      <c r="K14" s="27"/>
-      <c r="L14" s="32"/>
-      <c r="M14" s="33"/>
-      <c r="N14" s="34"/>
-      <c r="O14" s="35"/>
-      <c r="P14" s="36"/>
-      <c r="Q14" s="37"/>
-      <c r="R14" s="37"/>
-      <c r="S14" s="37"/>
-      <c r="T14" s="38"/>
-      <c r="U14" s="38"/>
-      <c r="V14" s="39"/>
-      <c r="W14" s="40"/>
-    </row>
-    <row r="15" ht="15" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A15" s="26"/>
-      <c r="B15" s="27"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="27"/>
-      <c r="H15" s="27"/>
-      <c r="I15" s="28"/>
-      <c r="J15" s="31"/>
-      <c r="K15" s="27"/>
-      <c r="L15" s="32"/>
-      <c r="M15" s="33"/>
-      <c r="N15" s="34"/>
-      <c r="O15" s="35"/>
-      <c r="P15" s="36"/>
-      <c r="Q15" s="37"/>
-      <c r="R15" s="37"/>
-      <c r="S15" s="37"/>
-      <c r="T15" s="38"/>
-      <c r="U15" s="38"/>
-      <c r="V15" s="39"/>
-      <c r="W15" s="40"/>
-    </row>
-    <row r="16" ht="15" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A16" s="26"/>
-      <c r="B16" s="27"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="29"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="27"/>
-      <c r="H16" s="27"/>
-      <c r="I16" s="28"/>
-      <c r="J16" s="31"/>
-      <c r="K16" s="27"/>
-      <c r="L16" s="32"/>
-      <c r="M16" s="33"/>
-      <c r="N16" s="34"/>
-      <c r="O16" s="35"/>
-      <c r="P16" s="36"/>
-      <c r="Q16" s="37"/>
-      <c r="R16" s="37"/>
-      <c r="S16" s="37"/>
-      <c r="T16" s="38"/>
-      <c r="U16" s="38"/>
-      <c r="V16" s="39"/>
-      <c r="W16" s="40"/>
-    </row>
-    <row r="17" ht="15" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A17" s="26"/>
-      <c r="B17" s="27"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="29"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="27"/>
-      <c r="H17" s="27"/>
-      <c r="I17" s="28"/>
-      <c r="J17" s="31"/>
-      <c r="K17" s="27"/>
-      <c r="L17" s="32"/>
-      <c r="M17" s="33"/>
-      <c r="N17" s="34"/>
-      <c r="O17" s="35"/>
-      <c r="P17" s="36"/>
-      <c r="Q17" s="37"/>
-      <c r="R17" s="37"/>
-      <c r="S17" s="37"/>
-      <c r="T17" s="38"/>
-      <c r="U17" s="38"/>
-      <c r="V17" s="39"/>
-      <c r="W17" s="40"/>
-    </row>
-    <row r="18" ht="15" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A18" s="26"/>
-      <c r="B18" s="27"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="29"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="27"/>
-      <c r="H18" s="27"/>
-      <c r="I18" s="28"/>
-      <c r="J18" s="31"/>
-      <c r="K18" s="27"/>
-      <c r="L18" s="32"/>
-      <c r="M18" s="33"/>
-      <c r="N18" s="34"/>
-      <c r="O18" s="35"/>
-      <c r="P18" s="36"/>
-      <c r="Q18" s="37"/>
-      <c r="R18" s="37"/>
-      <c r="S18" s="37"/>
-      <c r="T18" s="38"/>
-      <c r="U18" s="38"/>
-      <c r="V18" s="39"/>
-      <c r="W18" s="40"/>
-    </row>
-    <row r="19" ht="15" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A19" s="26"/>
-      <c r="B19" s="27"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="29"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="27"/>
-      <c r="H19" s="27"/>
-      <c r="I19" s="28"/>
-      <c r="J19" s="31"/>
-      <c r="K19" s="27"/>
-      <c r="L19" s="32"/>
-      <c r="M19" s="33"/>
-      <c r="N19" s="34"/>
-      <c r="O19" s="35"/>
-      <c r="P19" s="36"/>
-      <c r="Q19" s="37"/>
-      <c r="R19" s="37"/>
-      <c r="S19" s="37"/>
-      <c r="T19" s="38"/>
-      <c r="U19" s="38"/>
-      <c r="V19" s="39"/>
-      <c r="W19" s="40"/>
-    </row>
-    <row r="20" ht="15" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A20" s="26"/>
-      <c r="B20" s="42"/>
-      <c r="C20" s="42"/>
-      <c r="D20" s="43"/>
-      <c r="E20" s="29"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="42"/>
-      <c r="I20" s="43"/>
-      <c r="J20" s="45"/>
-      <c r="K20" s="42"/>
-      <c r="L20" s="46"/>
-      <c r="M20" s="47"/>
-      <c r="N20" s="34"/>
-      <c r="O20" s="48"/>
-      <c r="P20" s="49"/>
-      <c r="Q20" s="50"/>
-      <c r="R20" s="50"/>
-      <c r="S20" s="50"/>
-      <c r="T20" s="51"/>
-      <c r="U20" s="51"/>
-      <c r="V20" s="52"/>
-      <c r="W20" s="53"/>
-    </row>
-    <row r="21" ht="16.5" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A21" s="54" t="s">
-        <v>43</v>
-      </c>
-      <c r="B21" s="54"/>
-      <c r="C21" s="54"/>
-      <c r="D21" s="54"/>
-      <c r="E21" s="54"/>
-      <c r="F21" s="54"/>
-      <c r="G21" s="54"/>
-      <c r="H21" s="54"/>
-      <c r="I21" s="54"/>
-      <c r="J21" s="54"/>
-      <c r="K21" s="54"/>
-      <c r="L21" s="54"/>
-      <c r="M21" s="54"/>
-      <c r="N21" s="54"/>
-      <c r="O21" s="54"/>
-      <c r="P21" s="54"/>
-      <c r="Q21" s="54"/>
-      <c r="R21" s="54"/>
-      <c r="S21" s="54"/>
-      <c r="T21" s="54"/>
-      <c r="U21" s="54"/>
-      <c r="V21" s="54"/>
-      <c r="W21" s="54"/>
-    </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A22" s="55" t="s">
-        <v>44</v>
-      </c>
-      <c r="B22" s="55"/>
-      <c r="C22" s="55"/>
-      <c r="D22" s="55"/>
-      <c r="E22" s="55"/>
-      <c r="F22" s="55"/>
-      <c r="G22" s="55"/>
-      <c r="H22" s="55"/>
-      <c r="I22" s="55"/>
-      <c r="J22" s="55"/>
-      <c r="K22" s="55"/>
-      <c r="L22" s="55"/>
-      <c r="M22" s="55"/>
-      <c r="N22" s="55"/>
-      <c r="O22" s="55"/>
-      <c r="P22" s="55"/>
-      <c r="Q22" s="55"/>
-      <c r="R22" s="55"/>
-      <c r="S22" s="55"/>
-      <c r="T22" s="55"/>
-      <c r="U22" s="55"/>
-      <c r="V22" s="55"/>
-      <c r="W22" s="55"/>
-    </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A23" s="55" t="s">
-        <v>45</v>
-      </c>
-      <c r="B23" s="55"/>
-      <c r="C23" s="55"/>
-      <c r="D23" s="55"/>
-      <c r="E23" s="55"/>
-      <c r="F23" s="55"/>
-      <c r="G23" s="55"/>
-      <c r="H23" s="55"/>
-      <c r="I23" s="55"/>
-      <c r="J23" s="55"/>
-      <c r="K23" s="55"/>
-      <c r="L23" s="55"/>
-      <c r="M23" s="55"/>
-      <c r="N23" s="55"/>
-      <c r="O23" s="55"/>
-      <c r="P23" s="55"/>
-      <c r="Q23" s="55"/>
-      <c r="R23" s="55"/>
-      <c r="S23" s="55"/>
-      <c r="T23" s="55"/>
-      <c r="U23" s="55"/>
-      <c r="V23" s="55"/>
-      <c r="W23" s="55"/>
+      <c r="B23" s="60"/>
+      <c r="C23" s="60"/>
+      <c r="D23" s="60"/>
+      <c r="E23" s="60"/>
+      <c r="F23" s="60"/>
+      <c r="G23" s="60"/>
+      <c r="H23" s="60"/>
+      <c r="I23" s="60"/>
+      <c r="J23" s="60"/>
+      <c r="K23" s="60"/>
+      <c r="L23" s="60"/>
+      <c r="M23" s="60"/>
+      <c r="N23" s="60"/>
+      <c r="O23" s="60"/>
+      <c r="P23" s="60"/>
+      <c r="Q23" s="60"/>
+      <c r="R23" s="60"/>
+      <c r="S23" s="60"/>
+      <c r="T23" s="60"/>
+      <c r="U23" s="60"/>
+      <c r="V23" s="60"/>
+      <c r="W23" s="60"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" autoFilter="0"/>
   <mergeCells count="12">
+    <mergeCell ref="A22:W22"/>
+    <mergeCell ref="A23:W23"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="E4:I4"/>
+    <mergeCell ref="J4:M4"/>
+    <mergeCell ref="N4:W4"/>
+    <mergeCell ref="A21:W21"/>
     <mergeCell ref="B1:T3"/>
     <mergeCell ref="V1:W1"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="V2:W2"/>
     <mergeCell ref="U3:W3"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="E4:I4"/>
-    <mergeCell ref="J4:M4"/>
-    <mergeCell ref="N4:W4"/>
-    <mergeCell ref="A21:W21"/>
-    <mergeCell ref="A22:W22"/>
-    <mergeCell ref="A23:W23"/>
   </mergeCells>
-  <dataValidations count="24">
-    <dataValidation showInputMessage="1" showErrorMessage="1" sqref="B10:C20"/>
-    <dataValidation showInputMessage="1" showErrorMessage="1" sqref="B6:C20"/>
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Escriba el Número de su Contrato" error="Por Favor Escribir El Número De Su Contrato" sqref="D10:D20">
+  <dataValidations count="11">
+    <dataValidation showInputMessage="1" showErrorMessage="1" sqref="I6:I20 B6:C20" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Escriba el Número de su Contrato" error="Por Favor Escribir El Número De Su Contrato" sqref="D6:D20" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Escriba el Número de su Contrato" error="Por Favor Escribir El Número De Su Contrato" sqref="D6:D20">
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Escriba el Número de su Contrato" error="Por Favor Escribir El Número Del  Contrato Donde Esta Vinculado Actulamente El Beneficiario." sqref="G6:G20" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Escriba el Número de su Contrato" error="Por Favor Escribir El Número Del  Contrato Donde Esta Vinculado Actulamente El Beneficiario." sqref="G10:G20">
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Escriba el número de la UDS " error="Por Favor Escribir El Número De La UDS Donde Esta Vinculado Actulamente El Beneficiario." sqref="H6:H20" xr:uid="{00000000-0002-0000-0000-000006000000}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Escriba el Número de su Contrato" error="Por Favor Escribir El Número Del  Contrato Donde Esta Vinculado Actulamente El Beneficiario." sqref="G6:G20">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J6:J20" xr:uid="{00000000-0002-0000-0000-00000A000000}">
+      <formula1>"Cedula Ciudadanía, Cedula de Extranjería, Partida o Acta de Nacimiento, Pasaporte, Permiso Especial de Permanencia, Permiso por protección temporal, Registro Civil, Sin Documento, Tarjeta de Identidad, Tarjeta de Movilidad Fronteriza, VISA"</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K6:K20" xr:uid="{00000000-0002-0000-0000-00000C000000}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Escriba el número de la UDS " error="Por Favor Escribir El Número De La UDS Donde Esta Vinculado Actulamente El Beneficiario." sqref="H10:H20">
-      <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Escriba el número de la UDS " error="Por Favor Escribir El Número De La UDS Donde Esta Vinculado Actulamente El Beneficiario." sqref="H6:H20">
-      <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation showInputMessage="1" showErrorMessage="1" sqref="I10:I20"/>
-    <dataValidation showInputMessage="1" showErrorMessage="1" sqref="I6:I20"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J10:J20">
-      <formula1>"Cedula Ciudadanía, Cedula de Extranjería, Partida o Acta de Nacimiento, Pasaporte, Permiso Especial de Permanencia, Permiso por protección temporal, Registro Civil, Sin Documento, Tarjeta de Identidad, Tarjeta de Movilidad Fronteriza, VISA"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J6:J20">
-      <formula1>"Cedula Ciudadanía, Cedula de Extranjería, Partida o Acta de Nacimiento, Pasaporte, Permiso Especial de Permanencia, Permiso por protección temporal, Registro Civil, Sin Documento, Tarjeta de Identidad, Tarjeta de Movilidad Fronteriza, VISA"</formula1>
-    </dataValidation>
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K10:K20">
-      <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K6:K20">
-      <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation type="date" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="DD/MM/AAAA" error="El rango debe ser mayor al 01/01/2017" sqref="M10:M20">
+    <dataValidation type="date" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="DD/MM/AAAA" error="El rango debe ser mayor al 01/01/2017" sqref="M6:M20" xr:uid="{00000000-0002-0000-0000-00000E000000}">
       <formula1>43466</formula1>
     </dataValidation>
-    <dataValidation type="date" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="DD/MM/AAAA" error="El rango debe ser mayor al 01/01/2017" sqref="M6:M20">
-      <formula1>43466</formula1>
-    </dataValidation>
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="DD/MM/AAAA" error="El rango debe ser mayor al 01/01/2017" sqref="O10:P20">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="DD/MM/AAAA" error="El rango debe ser mayor al 01/01/2017" sqref="O6:P20" xr:uid="{00000000-0002-0000-0000-000010000000}">
       <formula1>42644</formula1>
       <formula2>43100</formula2>
     </dataValidation>
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="DD/MM/AAAA" error="El rango debe ser mayor al 01/01/2017" sqref="O6:P20">
-      <formula1>42644</formula1>
-      <formula2>43100</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q10:R20">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q6:R20" xr:uid="{00000000-0002-0000-0000-000012000000}">
       <formula1>"SI,NO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q6:R20">
-      <formula1>"SI,NO"</formula1>
-    </dataValidation>
-    <dataValidation type="date" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T10:U20">
+    <dataValidation type="date" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T6:U20" xr:uid="{00000000-0002-0000-0000-000014000000}">
       <formula1>43466</formula1>
     </dataValidation>
-    <dataValidation type="date" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T6:U20">
-      <formula1>43466</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V10:V20">
-      <formula1>"EN PROCESO,REMITIDO A OTRA REGIONAL, FINALIZADO"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V6:V20">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V6:V20" xr:uid="{00000000-0002-0000-0000-000016000000}">
       <formula1>"EN PROCESO,REMITIDO A OTRA REGIONAL, FINALIZADO"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="13" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" scale="13" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:I47"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="11.42578125"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="11.42578125" style="56" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" style="34" customWidth="1"/>
+    <col min="2" max="16384" width="11.42578125" style="34"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.45" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="57"/>
-      <c r="B1" s="57"/>
-      <c r="C1" s="58" t="s">
+    <row r="1" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="61"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="59" t="s">
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="60">
+      <c r="H1" s="63">
         <v>44728</v>
       </c>
-      <c r="I1" s="60"/>
-    </row>
-    <row r="2" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="57"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="59" t="s">
+      <c r="I1" s="63"/>
+    </row>
+    <row r="2" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="61"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="59" t="s">
+      <c r="H2" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="59"/>
-    </row>
-    <row r="3" ht="40.9" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="57"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58" t="s">
+      <c r="I2" s="64"/>
+    </row>
+    <row r="3" spans="1:9" ht="40.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="61"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+    </row>
+    <row r="4" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="66" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="66"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
+    </row>
+    <row r="5" spans="1:9" ht="104.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="67" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="67"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+    </row>
+    <row r="6" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="67" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="67"/>
+      <c r="C6" s="67"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="67"/>
+      <c r="H6" s="67"/>
+      <c r="I6" s="67"/>
+    </row>
+    <row r="7" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="68" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="68"/>
+      <c r="C7" s="68"/>
+      <c r="D7" s="68"/>
+      <c r="E7" s="68"/>
+      <c r="F7" s="68"/>
+      <c r="G7" s="68"/>
+      <c r="H7" s="68"/>
+      <c r="I7" s="68"/>
+    </row>
+    <row r="8" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="68"/>
+      <c r="B8" s="68"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="68"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="68"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="68"/>
+    </row>
+    <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="68"/>
+      <c r="B9" s="68"/>
+      <c r="C9" s="68"/>
+      <c r="D9" s="68"/>
+      <c r="E9" s="68"/>
+      <c r="F9" s="68"/>
+      <c r="G9" s="68"/>
+      <c r="H9" s="68"/>
+      <c r="I9" s="68"/>
+    </row>
+    <row r="10" spans="1:9" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="69"/>
+      <c r="B10" s="69"/>
+      <c r="C10" s="69"/>
+      <c r="D10" s="69"/>
+      <c r="E10" s="69"/>
+      <c r="F10" s="69"/>
+      <c r="G10" s="69"/>
+      <c r="H10" s="69"/>
+      <c r="I10" s="69"/>
+    </row>
+    <row r="11" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="70" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="70"/>
+      <c r="C11" s="70"/>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="71" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="71"/>
+      <c r="C12" s="71"/>
+      <c r="D12" s="71"/>
+      <c r="E12" s="71"/>
+      <c r="F12" s="71"/>
+      <c r="G12" s="71"/>
+      <c r="H12" s="71"/>
+      <c r="I12" s="71"/>
+    </row>
+    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="36"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" s="36"/>
+      <c r="F13" s="36"/>
+      <c r="G13" s="36"/>
+    </row>
+    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D14" s="34" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" s="34" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" s="34" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="H3" s="61"/>
-      <c r="I3" s="61"/>
-    </row>
-    <row r="4" ht="14.45" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="62" t="s">
+      <c r="D17" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="B4" s="62"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-    </row>
-    <row r="5" ht="104.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="63" t="s">
+    </row>
+    <row r="18" spans="2:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="63"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-    </row>
-    <row r="6" ht="43.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="63" t="s">
+      <c r="D18" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="B6" s="63"/>
-      <c r="C6" s="63"/>
-      <c r="D6" s="63"/>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="63"/>
-      <c r="I6" s="63"/>
-    </row>
-    <row r="7" ht="29.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="64" t="s">
+    </row>
+    <row r="19" spans="2:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="64"/>
-      <c r="C7" s="64"/>
-      <c r="D7" s="64"/>
-      <c r="E7" s="64"/>
-      <c r="F7" s="64"/>
-      <c r="G7" s="64"/>
-      <c r="H7" s="64"/>
-      <c r="I7" s="64"/>
-    </row>
-    <row r="8" ht="57" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="64"/>
-      <c r="B8" s="64"/>
-      <c r="C8" s="64"/>
-      <c r="D8" s="64"/>
-      <c r="E8" s="64"/>
-      <c r="F8" s="64"/>
-      <c r="G8" s="64"/>
-      <c r="H8" s="64"/>
-      <c r="I8" s="64"/>
-    </row>
-    <row r="9" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="64"/>
-      <c r="B9" s="64"/>
-      <c r="C9" s="64"/>
-      <c r="D9" s="64"/>
-      <c r="E9" s="64"/>
-      <c r="F9" s="64"/>
-      <c r="G9" s="64"/>
-      <c r="H9" s="64"/>
-      <c r="I9" s="64"/>
-    </row>
-    <row r="10" ht="47.45" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="65"/>
-      <c r="B10" s="65"/>
-      <c r="C10" s="65"/>
-      <c r="D10" s="65"/>
-      <c r="E10" s="65"/>
-      <c r="F10" s="65"/>
-      <c r="G10" s="65"/>
-      <c r="H10" s="65"/>
-      <c r="I10" s="65"/>
-    </row>
-    <row r="11" ht="16.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="66" t="s">
-        <v>43</v>
-      </c>
-      <c r="B11" s="66"/>
-      <c r="C11" s="66"/>
-      <c r="D11" s="66"/>
-      <c r="E11" s="66"/>
-      <c r="F11" s="66"/>
-      <c r="G11" s="66"/>
-      <c r="H11" s="66"/>
-      <c r="I11" s="66"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="67" t="s">
-        <v>44</v>
-      </c>
-      <c r="B12" s="67"/>
-      <c r="C12" s="67"/>
-      <c r="D12" s="67"/>
-      <c r="E12" s="67"/>
-      <c r="F12" s="67"/>
-      <c r="G12" s="67"/>
-      <c r="H12" s="67"/>
-      <c r="I12" s="67"/>
-    </row>
-    <row r="13" hidden="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="68"/>
-      <c r="B13" s="68"/>
-      <c r="C13" s="68"/>
-      <c r="D13" s="68" t="s">
+    </row>
+    <row r="20" spans="2:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="68"/>
-      <c r="F13" s="68"/>
-      <c r="G13" s="68"/>
-    </row>
-    <row r="14" hidden="1" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D14" s="56" t="s">
+      <c r="D20" s="34" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="15" hidden="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B15" s="69" t="s">
+    <row r="21" spans="2:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="37" t="s">
         <v>53</v>
       </c>
-      <c r="D15" s="56" t="s">
+      <c r="D21" s="34" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="16" hidden="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B16" s="69" t="s">
+    <row r="22" spans="2:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="37" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="56" t="s">
+      <c r="D22" s="34" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="17" hidden="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B17" s="69" t="s">
+    <row r="23" spans="2:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="D17" s="56" t="s">
+      <c r="D23" s="34" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="18" hidden="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18" s="69" t="s">
+    <row r="24" spans="2:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="D18" s="56" t="s">
+      <c r="D24" s="34" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="19" hidden="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B19" s="69" t="s">
-        <v>31</v>
-      </c>
-      <c r="D19" s="56" t="s">
+    <row r="25" spans="2:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="37" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="20" hidden="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B20" s="69" t="s">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B26" s="37" t="s">
         <v>62</v>
       </c>
-      <c r="D20" s="56" t="s">
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B27" s="37" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="21" hidden="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B21" s="69" t="s">
+    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B28" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="D21" s="56" t="s">
+    </row>
+    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B29" s="37" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="22" hidden="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B22" s="69" t="s">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B30" s="37" t="s">
         <v>66</v>
       </c>
-      <c r="D22" s="56" t="s">
+    </row>
+    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B31" s="37" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="23" hidden="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B23" s="69" t="s">
+    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B32" s="37" t="s">
         <v>68</v>
       </c>
-      <c r="D23" s="56" t="s">
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B33" s="37" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="24" hidden="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B24" s="69" t="s">
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B34" s="37" t="s">
         <v>70</v>
       </c>
-      <c r="D24" s="56" t="s">
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B35" s="37" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="25" hidden="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B25" s="69" t="s">
+    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B36" s="37" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B26" s="69" t="s">
+    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B37" s="37" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B27" s="69" t="s">
+    <row r="38" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B38" s="37" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B28" s="69" t="s">
+    <row r="39" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B39" s="37" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B29" s="69" t="s">
+    <row r="40" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B40" s="37" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B30" s="69" t="s">
+    <row r="41" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B41" s="37" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B31" s="69" t="s">
+    <row r="42" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B42" s="37" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B32" s="69" t="s">
+    <row r="43" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B43" s="37" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B33" s="69" t="s">
+    <row r="44" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B44" s="37" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B34" s="69" t="s">
+    <row r="45" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B45" s="37" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B35" s="69" t="s">
+    <row r="46" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B46" s="37" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B36" s="69" t="s">
+    <row r="47" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B47" s="37" t="s">
         <v>83</v>
-      </c>
-    </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B37" s="69" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B38" s="69" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B39" s="69" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B40" s="69" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B41" s="69" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B42" s="69" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="43" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B43" s="69" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B44" s="69" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="45" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B45" s="69" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="46" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B46" s="69" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="47" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B47" s="69" t="s">
-        <v>94</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A12:I12"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A6:I6"/>
+    <mergeCell ref="A7:I10"/>
+    <mergeCell ref="A11:I11"/>
     <mergeCell ref="A1:B3"/>
     <mergeCell ref="C1:F3"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="G3:I3"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="A6:I6"/>
-    <mergeCell ref="A7:I10"/>
-    <mergeCell ref="A11:I11"/>
-    <mergeCell ref="A12:I12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="87" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup scale="87" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>